--- a/data/trans_camb/P2A_enfcro_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 14,69</t>
+          <t>-6,55; 16,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 7,94</t>
+          <t>-14,46; 9,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45,74; 65,79</t>
+          <t>46,11; 66,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 16,24</t>
+          <t>-7,31; 16,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 12,55</t>
+          <t>-11,2; 11,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,57; 69,99</t>
+          <t>52,18; 69,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 13,94</t>
+          <t>-3,37; 12,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 5,94</t>
+          <t>-10,25; 5,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,18; 65,79</t>
+          <t>52,04; 65,23</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,47; 51,95</t>
+          <t>-15,59; 58,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,49; 30,43</t>
+          <t>-34,8; 34,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106,14; 238,69</t>
+          <t>109,31; 244,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 53,77</t>
+          <t>-16,62; 52,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 41,54</t>
+          <t>-26,03; 37,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>114,5; 250,73</t>
+          <t>116,13; 246,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 44,49</t>
+          <t>-8,81; 38,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 19,21</t>
+          <t>-25,28; 18,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>123,52; 217,56</t>
+          <t>125,56; 213,38</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 19,26</t>
+          <t>2,32; 19,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 11,84</t>
+          <t>-5,6; 11,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53,7; 66,35</t>
+          <t>54,18; 65,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 16,02</t>
+          <t>-1,34; 14,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 5,57</t>
+          <t>-9,16; 5,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,09; 61,82</t>
+          <t>49,24; 62,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 14,99</t>
+          <t>2,78; 15,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 6,29</t>
+          <t>-5,02; 6,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53,34; 62,98</t>
+          <t>52,77; 62,05</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 62,11</t>
+          <t>6,23; 63,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 37,07</t>
+          <t>-14,41; 38,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>129,91; 217,74</t>
+          <t>134,35; 221,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 48,71</t>
+          <t>-3,95; 45,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,65; 16,48</t>
+          <t>-22,1; 16,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>116,64; 193,11</t>
+          <t>115,92; 194,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 45,4</t>
+          <t>7,61; 46,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 19,06</t>
+          <t>-12,63; 20,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>132,08; 193,09</t>
+          <t>131,05; 189,87</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 14,14</t>
+          <t>-9,1; 16,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 6,32</t>
+          <t>-14,95; 7,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,41; 54,31</t>
+          <t>36,56; 55,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 10,52</t>
+          <t>-11,67; 11,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 6,52</t>
+          <t>-14,4; 7,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,44; 54,52</t>
+          <t>37,47; 54,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 8,9</t>
+          <t>-7,43; 9,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 3,2</t>
+          <t>-12,04; 3,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40,12; 52,04</t>
+          <t>39,7; 51,86</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 33,41</t>
+          <t>-16,51; 41,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,72; 14,81</t>
+          <t>-27,4; 18,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63,66; 133,21</t>
+          <t>64,47; 141,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,79; 23,52</t>
+          <t>-22,28; 26,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,69; 15,17</t>
+          <t>-26,18; 16,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>64,81; 132,14</t>
+          <t>65,6; 131,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 20,4</t>
+          <t>-14,05; 21,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,33; 7,08</t>
+          <t>-22,38; 7,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74,19; 121,91</t>
+          <t>71,26; 118,97</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 16,88</t>
+          <t>-3,0; 17,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 21,55</t>
+          <t>1,41; 21,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46,07; 60,1</t>
+          <t>45,87; 60,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 17,64</t>
+          <t>-0,76; 18,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 8,99</t>
+          <t>-10,83; 9,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,31; 53,24</t>
+          <t>38,59; 51,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 14,25</t>
+          <t>1,22; 15,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 12,67</t>
+          <t>-2,04; 12,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44,54; 54,25</t>
+          <t>44,7; 54,3</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 43,8</t>
+          <t>-6,37; 46,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 57,46</t>
+          <t>3,22; 54,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94,5; 164,78</t>
+          <t>91,43; 165,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 41,54</t>
+          <t>-0,72; 41,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 20,67</t>
+          <t>-20,11; 20,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,54; 124,94</t>
+          <t>71,64; 121,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,01; 33,47</t>
+          <t>2,53; 36,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 29,87</t>
+          <t>-4,12; 28,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>88,79; 132,23</t>
+          <t>89,17; 132,33</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,14; 12,01</t>
+          <t>1,3; 11,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 7,43</t>
+          <t>-2,2; 7,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51,31; 59,17</t>
+          <t>51,67; 59,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 10,25</t>
+          <t>-0,08; 9,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 3,11</t>
+          <t>-6,51; 3,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,92; 55,59</t>
+          <t>48,12; 55,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,46; 9,48</t>
+          <t>2,43; 9,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 3,7</t>
+          <t>-3,34; 3,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>51,08; 55,96</t>
+          <t>50,57; 56,07</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5,2; 32,59</t>
+          <t>3,02; 31,24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 19,49</t>
+          <t>-5,32; 21,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118,3; 163,26</t>
+          <t>119,88; 162,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,67; 25,45</t>
+          <t>-0,18; 24,89</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 7,59</t>
+          <t>-14,91; 7,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>103,22; 139,85</t>
+          <t>104,49; 141,65</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,71; 23,8</t>
+          <t>5,42; 24,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 9,45</t>
+          <t>-7,67; 9,79</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>116,95; 142,41</t>
+          <t>115,41; 144,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 16,25</t>
+          <t>-8,48; 14,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 9,2</t>
+          <t>-14,83; 7,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46,11; 66,38</t>
+          <t>44,77; 65,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 16,56</t>
+          <t>-5,67; 17,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 11,26</t>
+          <t>-9,88; 11,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,18; 69,84</t>
+          <t>52,57; 69,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 12,45</t>
+          <t>-2,69; 13,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 5,71</t>
+          <t>-9,34; 6,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,04; 65,23</t>
+          <t>52,05; 65,05</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 58,78</t>
+          <t>-19,83; 53,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,8; 34,11</t>
+          <t>-37,7; 26,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109,31; 244,75</t>
+          <t>102,97; 236,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 52,76</t>
+          <t>-13,44; 56,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 37,27</t>
+          <t>-23,35; 39,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>116,13; 246,48</t>
+          <t>116,67; 240,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 38,98</t>
+          <t>-6,62; 43,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 18,0</t>
+          <t>-23,92; 20,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>125,56; 213,38</t>
+          <t>126,39; 216,39</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 19,38</t>
+          <t>2,38; 19,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 11,54</t>
+          <t>-5,15; 11,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54,18; 65,62</t>
+          <t>53,67; 66,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 14,98</t>
+          <t>-0,97; 15,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 5,42</t>
+          <t>-8,84; 6,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,24; 62,3</t>
+          <t>49,8; 62,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 15,42</t>
+          <t>2,87; 14,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 6,7</t>
+          <t>-5,29; 6,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52,77; 62,05</t>
+          <t>53,48; 62,5</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,23; 63,32</t>
+          <t>6,0; 61,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 38,0</t>
+          <t>-13,39; 36,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134,35; 221,53</t>
+          <t>133,3; 220,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 45,07</t>
+          <t>-2,59; 47,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 16,42</t>
+          <t>-21,79; 19,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>115,92; 194,24</t>
+          <t>118,81; 201,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,61; 46,36</t>
+          <t>7,25; 44,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 20,1</t>
+          <t>-13,35; 20,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>131,05; 189,87</t>
+          <t>134,75; 193,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 16,79</t>
+          <t>-8,99; 14,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 7,55</t>
+          <t>-14,8; 7,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,56; 55,93</t>
+          <t>36,38; 55,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 11,44</t>
+          <t>-10,83; 12,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 7,13</t>
+          <t>-15,03; 6,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,47; 54,39</t>
+          <t>37,02; 54,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 9,82</t>
+          <t>-6,65; 10,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 3,59</t>
+          <t>-11,34; 3,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,7; 51,86</t>
+          <t>39,22; 51,65</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,51; 41,79</t>
+          <t>-16,41; 35,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,4; 18,92</t>
+          <t>-26,92; 17,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64,47; 141,15</t>
+          <t>63,98; 138,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 26,39</t>
+          <t>-19,99; 29,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 16,26</t>
+          <t>-27,91; 14,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65,6; 131,95</t>
+          <t>64,77; 132,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 21,92</t>
+          <t>-12,56; 22,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 7,77</t>
+          <t>-21,32; 7,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71,26; 118,97</t>
+          <t>71,27; 118,45</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 17,44</t>
+          <t>-3,18; 16,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 21,21</t>
+          <t>0,77; 21,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45,87; 60,11</t>
+          <t>45,86; 59,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 18,1</t>
+          <t>-1,15; 18,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 9,03</t>
+          <t>-10,7; 9,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,59; 51,97</t>
+          <t>38,33; 53,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 15,33</t>
+          <t>1,0; 14,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 12,39</t>
+          <t>-1,28; 12,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44,7; 54,3</t>
+          <t>44,53; 54,67</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 46,02</t>
+          <t>-7,07; 43,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,22; 54,9</t>
+          <t>1,92; 56,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91,43; 165,15</t>
+          <t>92,9; 162,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 41,19</t>
+          <t>-2,2; 40,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 20,42</t>
+          <t>-20,97; 22,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,64; 121,34</t>
+          <t>68,46; 125,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,53; 36,86</t>
+          <t>1,92; 33,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 28,74</t>
+          <t>-2,72; 29,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>89,17; 132,33</t>
+          <t>87,65; 132,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 11,69</t>
+          <t>1,66; 11,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 7,93</t>
+          <t>-1,93; 7,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51,67; 59,09</t>
+          <t>51,66; 59,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 9,98</t>
+          <t>0,74; 10,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 3,05</t>
+          <t>-6,86; 3,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48,12; 55,69</t>
+          <t>48,09; 55,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,43; 9,85</t>
+          <t>2,51; 9,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 3,85</t>
+          <t>-3,24; 3,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>50,57; 56,07</t>
+          <t>51,03; 56,55</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3,02; 31,24</t>
+          <t>4,02; 31,91</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 21,54</t>
+          <t>-4,77; 21,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119,88; 162,57</t>
+          <t>119,96; 163,23</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 24,89</t>
+          <t>1,49; 26,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 7,42</t>
+          <t>-15,01; 8,38</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>104,49; 141,65</t>
+          <t>103,95; 140,02</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,42; 24,75</t>
+          <t>5,73; 24,53</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 9,79</t>
+          <t>-7,53; 9,24</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>115,41; 144,12</t>
+          <t>117,79; 146,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,79</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,79</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>61,35</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4,46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-3,46</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>56,93</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,79</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,21</t>
+          <t>57,6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>59,12</t>
+          <t>59,38</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 14,76</t>
+          <t>-5,4; 16,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 7,9</t>
+          <t>-10,52; 12,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,77; 65,91</t>
+          <t>51,84; 70,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 17,13</t>
+          <t>-8,54; 14,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 11,77</t>
+          <t>-14,3; 7,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,57; 69,5</t>
+          <t>45,98; 66,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 13,72</t>
+          <t>-2,12; 13,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 6,42</t>
+          <t>-10,15; 5,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,05; 65,05</t>
+          <t>52,32; 65,86</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>167,47%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>12,81%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-9,97%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>163,75%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15,8%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>167,08%</t>
+          <t>165,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>165,33%</t>
+          <t>166,07%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,83; 53,2</t>
+          <t>-12,75; 53,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,7; 26,94</t>
+          <t>-24,75; 41,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>102,97; 236,65</t>
+          <t>113,93; 247,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 56,39</t>
+          <t>-19,47; 51,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 39,38</t>
+          <t>-35,49; 30,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>116,67; 240,99</t>
+          <t>107,92; 240,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 43,58</t>
+          <t>-5,4; 44,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,92; 20,89</t>
+          <t>-24,21; 19,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>126,39; 216,39</t>
+          <t>124,65; 217,81</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,91</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,84</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>56,75</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>10,9</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,31</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>60,29</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,91</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,84</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,08</t>
+          <t>59,93</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>58,09</t>
+          <t>58,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 19,27</t>
+          <t>-0,76; 16,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 11,73</t>
+          <t>-9,43; 5,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53,67; 66,04</t>
+          <t>49,85; 62,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 15,42</t>
+          <t>1,51; 19,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 6,08</t>
+          <t>-5,25; 11,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,8; 62,8</t>
+          <t>53,21; 66,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 14,94</t>
+          <t>3,24; 14,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 6,5</t>
+          <t>-5,19; 6,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53,48; 62,5</t>
+          <t>53,57; 62,99</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18,61%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-4,96%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>152,79%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>30,67%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>9,32%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>169,62%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18,61%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-4,96%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>150,97%</t>
+          <t>168,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>159,82%</t>
+          <t>160,41%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,0; 61,93</t>
+          <t>-1,94; 48,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 36,16</t>
+          <t>-22,65; 16,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133,3; 220,42</t>
+          <t>118,14; 195,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 47,52</t>
+          <t>3,64; 62,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 19,18</t>
+          <t>-12,88; 37,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>118,81; 201,77</t>
+          <t>128,89; 217,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 44,47</t>
+          <t>8,3; 45,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 20,01</t>
+          <t>-13,27; 19,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>134,75; 193,55</t>
+          <t>133,81; 194,36</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,26</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-3,65</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>45,65</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>3,1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,08</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>46,08</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,65</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45,84</t>
+          <t>46,05</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45,95</t>
+          <t>45,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 14,53</t>
+          <t>-13,49; 10,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 7,01</t>
+          <t>-13,87; 6,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,38; 55,0</t>
+          <t>37,21; 54,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 12,29</t>
+          <t>-10,02; 14,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 6,39</t>
+          <t>-15,08; 6,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,02; 54,76</t>
+          <t>36,27; 54,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 10,06</t>
+          <t>-6,26; 8,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 3,19</t>
+          <t>-11,52; 3,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,22; 51,65</t>
+          <t>40,0; 52,0</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-7,41%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>92,8%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>6,43%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-8,46%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>95,62%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-7,41%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 35,92</t>
+          <t>-23,79; 23,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,92; 17,74</t>
+          <t>-25,69; 15,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63,98; 138,66</t>
+          <t>64,89; 132,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,99; 29,55</t>
+          <t>-17,94; 33,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,91; 14,71</t>
+          <t>-27,72; 14,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>64,77; 132,17</t>
+          <t>63,77; 133,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 22,93</t>
+          <t>-12,03; 20,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 7,04</t>
+          <t>-21,33; 7,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71,27; 118,45</t>
+          <t>74,09; 121,73</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8,51</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>45,4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6,84</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>11,4</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>53,2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8,51</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,67</t>
+          <t>52,75</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>49,44</t>
+          <t>49,08</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 16,33</t>
+          <t>-1,57; 17,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 21,38</t>
+          <t>-9,94; 8,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45,86; 59,62</t>
+          <t>38,91; 52,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 18,76</t>
+          <t>-3,62; 16,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 9,42</t>
+          <t>0,66; 21,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,33; 53,41</t>
+          <t>45,72; 59,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 14,45</t>
+          <t>0,93; 14,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 12,24</t>
+          <t>-1,86; 12,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>44,53; 54,67</t>
+          <t>44,12; 53,98</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>17,29%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-1,12%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>92,2%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>15,99%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>26,67%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>124,41%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>17,29%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-1,12%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>123,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>107,56%</t>
+          <t>106,76%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 43,61</t>
+          <t>-2,22; 41,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 56,49</t>
+          <t>-18,99; 20,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>92,9; 162,25</t>
+          <t>71,05; 124,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 40,88</t>
+          <t>-7,98; 43,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,97; 22,07</t>
+          <t>1,92; 57,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>68,46; 125,05</t>
+          <t>93,09; 162,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 33,88</t>
+          <t>2,01; 33,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 29,25</t>
+          <t>-3,83; 29,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>87,65; 132,51</t>
+          <t>87,54; 130,25</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,28</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,72</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>51,97</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>6,86</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2,62</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>55,36</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,28</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,72</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,97</t>
+          <t>55,12</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>53,62</t>
+          <t>53,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 11,84</t>
+          <t>0,78; 10,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 7,82</t>
+          <t>-6,55; 3,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51,66; 59,35</t>
+          <t>48,03; 55,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 10,59</t>
+          <t>2,14; 12,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 3,39</t>
+          <t>-2,49; 7,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48,09; 55,62</t>
+          <t>50,96; 58,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,51; 9,75</t>
+          <t>2,46; 9,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,72</t>
+          <t>-3,25; 3,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>51,03; 56,55</t>
+          <t>50,87; 55,9</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>12,34%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-4,01%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>121,42%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>17,27%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>6,59%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>139,23%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>12,34%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-4,01%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>121,43%</t>
+          <t>138,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>129,77%</t>
+          <t>129,5%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4,02; 31,91</t>
+          <t>1,67; 25,45</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 21,29</t>
+          <t>-14,48; 7,59</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>119,96; 163,23</t>
+          <t>103,51; 140,34</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1,49; 26,05</t>
+          <t>5,2; 32,59</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 8,38</t>
+          <t>-5,99; 19,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>103,95; 140,02</t>
+          <t>117,52; 162,48</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,73; 24,53</t>
+          <t>5,71; 23,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 9,24</t>
+          <t>-7,52; 9,45</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>117,79; 146,31</t>
+          <t>116,91; 142,37</t>
         </is>
       </c>
     </row>
